--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED01.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED01.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>169W</t>
+          <t>91W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N3"/>
+  <dimension ref="B2:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,6 +917,18 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1季</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>122W</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1767,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0019</t>
+          <t>SIM_XA_FIXED-4-0161</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1769,11 +1781,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30W</t>
+          <t>122W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1793,7 +1805,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1815,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2141,10 +2153,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2165,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2182,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2208,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2234,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,7 +2260,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2274,7 +2286,7 @@
         <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2326,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2349,10 +2361,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E22" t="n">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2373,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2390,7 @@
         <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2404,7 +2416,7 @@
         <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2430,7 +2442,7 @@
         <v>-8</v>
       </c>
       <c r="E25" t="n">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2456,7 +2468,7 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2482,7 +2494,7 @@
         <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2508,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2534,7 +2546,7 @@
         <v>-12</v>
       </c>
       <c r="E29" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2560,7 +2572,7 @@
         <v>-8</v>
       </c>
       <c r="E30" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2586,7 +2598,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2612,7 +2624,7 @@
         <v>-15</v>
       </c>
       <c r="E32" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2638,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2664,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2687,10 +2699,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E35" t="n">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2699,7 +2711,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2728,7 @@
         <v>-14</v>
       </c>
       <c r="E36" t="n">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2742,7 +2754,7 @@
         <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2768,7 +2780,7 @@
         <v>25</v>
       </c>
       <c r="E38" t="n">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2787,14 +2799,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2803,7 +2815,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0019", "receivable_term_quarters": 0, "revenue_wan": 30.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2817,19 +2829,19 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-12</v>
+        <v>-24</v>
       </c>
       <c r="E40" t="n">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2843,19 +2855,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="E41" t="n">
-        <v>281</v>
+        <v>241</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-9ba62a59ce", "line_id": "L-e63e17c32e", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-7bf4dcf2a0", "line_id": "L-e63e17c32e", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2872,11 +2884,11 @@
         <v>-14</v>
       </c>
       <c r="E42" t="n">
-        <v>267</v>
+        <v>227</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2891,14 +2903,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E43" t="n">
-        <v>253</v>
+        <v>212</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2907,7 +2919,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-e63e17c32e"}</t>
         </is>
       </c>
     </row>
@@ -2917,14 +2929,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2933,7 +2945,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-e63e17c32e"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-e63e17c32e", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2959,7 +2971,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-e63e17c32e", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-e63e17c32e", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2969,23 +2981,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E46" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-e63e17c32e", "asset_type": "production_line"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2995,14 +3007,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3011,7 +3023,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3021,23 +3033,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0161", "receivable_term_quarters": 3, "revenue_wan": 122.0}</t>
         </is>
       </c>
     </row>
@@ -3047,14 +3059,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-14</v>
+        <v>-36</v>
       </c>
       <c r="E49" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3063,7 +3075,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -3073,23 +3085,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E50" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-9996130b47", "line_id": "L-e63e17c32e", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -3099,23 +3111,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E51" t="n">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-e63e17c32e"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3125,23 +3137,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E52" t="n">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-e63e17c32e", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3151,21 +3163,73 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>91</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-e63e17c32e"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>169</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>91</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-e63e17c32e", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>91</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-e63e17c32e", "asset_type": "production_line"}</t>
         </is>
@@ -3272,16 +3336,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3497,16 +3561,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3565,10 +3629,10 @@
         <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17">
@@ -3590,10 +3654,10 @@
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -3615,10 +3679,10 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -3634,16 +3698,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3659,16 +3723,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-78</v>
+        <v>-70</v>
       </c>
       <c r="G20" t="n">
-        <v>-73</v>
+        <v>-75</v>
       </c>
       <c r="H20" t="n">
-        <v>-69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -3709,16 +3773,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-93.2</v>
+        <v>-85.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-88.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-84.2</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="23">
@@ -3759,16 +3823,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-93.2</v>
+        <v>-85.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-88.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-84.2</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="25">
@@ -3809,16 +3873,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-93.2</v>
+        <v>-85.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-88.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-84.2</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="28">
@@ -3908,16 +3972,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F30" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G30" t="n">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="H30" t="n">
-        <v>169</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
@@ -3942,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
@@ -3964,7 +4028,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3992,7 +4056,7 @@
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
@@ -4033,16 +4097,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F35" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="G35" t="n">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="H35" t="n">
-        <v>189</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36">
@@ -4158,16 +4222,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>490.6</v>
+        <v>498.6</v>
       </c>
       <c r="F40" t="n">
-        <v>397.4</v>
+        <v>413.4</v>
       </c>
       <c r="G40" t="n">
-        <v>309.2</v>
+        <v>323.2</v>
       </c>
       <c r="H40" t="n">
-        <v>225</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41">
@@ -4336,13 +4400,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-184.4</v>
+        <v>-176.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-277.6</v>
+        <v>-261.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-365.8</v>
+        <v>-351.8</v>
       </c>
     </row>
     <row r="48">
@@ -4358,16 +4422,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-93.2</v>
+        <v>-85.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-88.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-84.2</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="49">
@@ -4383,16 +4447,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>490.6</v>
+        <v>498.6</v>
       </c>
       <c r="F49" t="n">
-        <v>397.4</v>
+        <v>413.4</v>
       </c>
       <c r="G49" t="n">
-        <v>309.2</v>
+        <v>323.2</v>
       </c>
       <c r="H49" t="n">
-        <v>225</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50">
@@ -4408,16 +4472,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>490.6</v>
+        <v>498.6</v>
       </c>
       <c r="F50" t="n">
-        <v>397.4</v>
+        <v>413.4</v>
       </c>
       <c r="G50" t="n">
-        <v>309.2</v>
+        <v>323.2</v>
       </c>
       <c r="H50" t="n">
-        <v>225</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4488,7 +4552,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4637,7 +4701,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4786,7 +4850,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4935,7 +4999,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5084,7 +5148,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
